--- a/api/templates/device_utilization/es.xlsx
+++ b/api/templates/device_utilization/es.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="21126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24931"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl$\Ubuntu-20.04\home\ubuntu\aspect\api\templates\device_capacity\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl$\Ubuntu\home\stefan\aspect\api\templates\device_utilization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F3AA4B0-D08F-4438-9911-1DCCA419D6E0}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B7D32D2-085E-497E-93F9-41E59CAD4561}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="35570" yWindow="1330" windowWidth="22990" windowHeight="16080" tabRatio="815" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1131" yWindow="746" windowWidth="25946" windowHeight="17768" tabRatio="815" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Activity" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -84,6 +84,13 @@
       <sz val="12"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -123,7 +130,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="43">
+  <cellStyleXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -167,15 +174,17 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="43" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="43">
+  <cellStyles count="44">
     <cellStyle name="Followed Hyperlink" xfId="2" builtinId="9" hidden="1"/>
     <cellStyle name="Followed Hyperlink" xfId="4" builtinId="9" hidden="1"/>
     <cellStyle name="Followed Hyperlink" xfId="6" builtinId="9" hidden="1"/>
@@ -219,6 +228,7 @@
     <cellStyle name="Hyperlink" xfId="39" builtinId="8" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="41" builtinId="8" hidden="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="43" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
@@ -556,45 +566,45 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A8"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.9" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="31.83203125" customWidth="1"/>
+    <col min="1" max="1" width="31.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="21" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:1" ht="20.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A5" s="1"/>
     </row>
-    <row r="6" spans="1:1" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:1" ht="16.3" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A6" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:1" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A7" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:1" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A8" s="4" t="s">
         <v>1</v>
       </c>

--- a/api/templates/device_utilization/es.xlsx
+++ b/api/templates/device_utilization/es.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ahernandez/repos/aspect/api/templates/device_utilization/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FC36F66-6F3A-D845-9835-EA86F388D3D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85033D61-498E-684F-9F64-472655FE90F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="16380" windowHeight="8200" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>Entre fechas: &lt;Dates&gt;</t>
   </si>
@@ -52,6 +52,12 @@
   </si>
   <si>
     <t>Utilización de dispositivos</t>
+  </si>
+  <si>
+    <t>&lt;dailyTestCapacity&gt;</t>
+  </si>
+  <si>
+    <t>Capacidad Diaria</t>
   </si>
 </sst>
 </file>
@@ -131,7 +137,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -142,6 +148,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -599,19 +609,25 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>5</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>6</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/api/templates/device_utilization/es.xlsx
+++ b/api/templates/device_utilization/es.xlsx
@@ -1,35 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ahernandez/repos/aspect/api/templates/device_utilization/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85033D61-498E-684F-9F64-472655FE90F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="16380" windowHeight="8200" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="16380" windowHeight="8200"/>
   </bookViews>
   <sheets>
-    <sheet name="Tasa de Utilización" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Tasa de Utilización" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+  <si>
+    <t>Utilización de dispositivos</t>
+  </si>
   <si>
     <t>Entre fechas: &lt;Dates&gt;</t>
   </si>
   <si>
+    <t>Los porcentajes por dispositivo no están ponderados según su capacidad. Por eso, el promedio simple de estos valores puede diferir del porcentaje total mostrado en el sistema.</t>
+  </si>
+  <si>
     <t>Estados: &lt;States&gt;</t>
   </si>
   <si>
@@ -45,54 +40,54 @@
     <t>Dispositivos</t>
   </si>
   <si>
+    <t>Sitio</t>
+  </si>
+  <si>
+    <t>Capacidad Diaria</t>
+  </si>
+  <si>
     <t>&lt;name&gt;</t>
   </si>
   <si>
-    <t>Los porcentajes por dispositivo no están ponderados según su capacidad. Por eso, el promedio simple de estos valores puede diferir del porcentaje total mostrado en el sistema.</t>
-  </si>
-  <si>
-    <t>Utilización de dispositivos</t>
+    <t>&lt;siteName&gt;</t>
   </si>
   <si>
     <t>&lt;dailyTestCapacity&gt;</t>
-  </si>
-  <si>
-    <t>Capacidad Diaria</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
+      <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+      <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
+      <charset val="1"/>
+      <color rgb="FF000000"/>
+      <family val="2"/>
       <sz val="16"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <charset val="1"/>
       <color rgb="FF000000"/>
+      <family val="2"/>
+      <sz val="12"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
+      <charset val="1"/>
+      <family val="2"/>
       <sz val="12"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -118,115 +113,37 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="medium"/>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF3CC0DD"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF333333"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -554,87 +471,103 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J11"/>
+  <sheetFormatPr defaultRowHeight="16" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" defaultColWidth="11" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="31.83203125" customWidth="1"/>
+    <col min="2" max="2" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+    <row r="1" ht="21" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+    </row>
+    <row r="5" ht="17" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" ht="17" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" ht="33" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-    </row>
-    <row r="5" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8" s="6" t="s">
+      <c r="C8" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>9</v>
-      </c>
-    </row>
+      <c r="B9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="C2:I4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>